--- a/surveyor_forms/001_net_promoter_score_form--surveyor_forms.xlsx
+++ b/surveyor_forms/001_net_promoter_score_form--surveyor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>net_promoter_score_form</t>
+          <t>net_promoter_score</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -584,23 +584,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>customer_feelings_2</t>
+          <t>referral_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>On a scale of 0-10, how likely are you to recommend this company?</t>
+          <t>Referrals - how often do you usually refer a friend to this company?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_feelings_3</t>
+          <t>customer_referrals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How likely are you to recommend this company?</t>
+          <t>How likely are you to refer a friend to this company?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>customer_referrals</t>
+          <t>satisfaction_level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How likely are you to refer a friend to this company?</t>
+          <t>On a scale of 0-10, how satisfied are you with this company?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>customer_referrals_2</t>
+          <t>loyalty_level</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How likely are you to refer a friend to this company?</t>
+          <t>How likely are you to be a loyal customer?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,23 +676,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>customer_referrals_3</t>
+          <t>retention_level</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Referrals</t>
+          <t>How likely are you to continue using this company?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>customer_referrals_4</t>
+          <t>recommendation_level</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How likely are you to refer a friend to this company?</t>
+          <t>How likely are you to recommend this company?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,62 +727,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>customer_feelings_2_2</t>
+          <t>customer_referrals_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>On a scale of 0-10, how likely are you to recommend this company?</t>
+          <t>How often do you usually recommend this company?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>customer_feelings_3_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>How likely are you to recommend this company?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>customer_feelings_4</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>On a scale of 0-10, how likely are you to recommend this company?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -802,9 +756,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,102 +781,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_referrals_3_choices</t>
+          <t>referral_frequency_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_0,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 0, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_referrals_3_choices</t>
+          <t>referral_frequency_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>customer_referrals_3_choices</t>
+          <t>referral_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>customer_referrals_3_choices</t>
+          <t>referral_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>customer_referrals_3_choices</t>
+          <t>referral_frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Almost always'}</t>
+          <t>Almost always</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>customer_referrals_3_choices</t>
+          <t>referral_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
